--- a/tasks/tasks.xlsx
+++ b/tasks/tasks.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>Дата</t>
   </si>
@@ -155,6 +155,55 @@
 1) функция фильтрации
 2) функция добавление фильтра
 3) функция удаление фильтра</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1) добавил </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>bucket</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (стили, поведение)
+2) настроил поведение </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>filters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+3) исправил баг с меню</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -242,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -277,6 +326,18 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -604,7 +665,7 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="13">
         <v>46312</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -625,7 +686,7 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
@@ -746,11 +807,17 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>46326</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="13"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -759,11 +826,13 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+    <row r="11" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>46327</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1272,8 +1341,11 @@
       <c r="K50" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
